--- a/diseases/d058/2026-2029.xlsx
+++ b/diseases/d058/2026-2029.xlsx
@@ -9058,12 +9058,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -9088,22 +9088,22 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -9136,40 +9136,185 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA59" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>scrub-typhus</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>恙虫病</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>1</v>
+      </c>
+      <c r="O60" t="n">
+        <v>1</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.001937969923792046</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr"/>
+      <c r="AT60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV60" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW59" t="inlineStr">
+      <c r="AW60" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
+      <c r="AX60" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY59" t="inlineStr">
+      <c r="AY60" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
+      <c r="AZ60" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA59" t="inlineStr">
+      <c r="BA60" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB59" t="inlineStr">
+      <c r="BB60" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC59" t="inlineStr">
+      <c r="BC60" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -9291,7 +9436,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10">
@@ -9301,7 +9446,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d058/2026-2029.xlsx
+++ b/diseases/d058/2026-2029.xlsx
@@ -8227,13 +8227,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O53" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R53" t="n">
-        <v>0.03100751878067274</v>
+        <v>0.03294548870446478</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -9242,13 +9242,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R60" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d058/2026-2029.xlsx
+++ b/diseases/d058/2026-2029.xlsx
@@ -9242,13 +9242,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R60" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d058/2026-2029.xlsx
+++ b/diseases/d058/2026-2029.xlsx
@@ -9242,13 +9242,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R60" t="n">
-        <v>0.005813909771376137</v>
+        <v>0.009689849618960231</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -9317,6 +9317,151 @@
       <c r="BC60" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>scrub-typhus</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>恙虫病</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" t="n">
+        <v>1</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP61" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr"/>
+      <c r="AT61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV61" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA61" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB61" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC61" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -9353,7 +9498,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -9436,7 +9581,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
@@ -9446,7 +9591,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
@@ -9498,7 +9643,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d058/2026-2029.xlsx
+++ b/diseases/d058/2026-2029.xlsx
@@ -9242,13 +9242,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O60" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R60" t="n">
-        <v>0.009689849618960231</v>
+        <v>0.01356578946654432</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d058/2026-2029.xlsx
+++ b/diseases/d058/2026-2029.xlsx
@@ -9242,13 +9242,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R60" t="n">
-        <v>0.01356578946654432</v>
+        <v>0.01550375939033637</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d058/2026-2029.xlsx
+++ b/diseases/d058/2026-2029.xlsx
@@ -9242,13 +9242,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R60" t="n">
-        <v>0.01550375939033637</v>
+        <v>0.01744172931412841</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d058/2026-2029.xlsx
+++ b/diseases/d058/2026-2029.xlsx
@@ -8188,12 +8188,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -8227,13 +8227,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>0.03294548870446478</v>
+        <v>0.01355270280196709</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -8266,42 +8266,42 @@
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8333,12 +8333,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -8372,13 +8372,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="O54" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="R54" t="n">
-        <v>0.02172846223218448</v>
+        <v>0.03294548870446478</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -8411,42 +8411,42 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -8478,12 +8478,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -8517,13 +8517,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>0.02172846223218448</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -8556,42 +8556,42 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -9203,12 +9203,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -9233,22 +9233,22 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>0.01744172931412841</v>
+        <v>0</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -9281,42 +9281,42 @@
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -9348,12 +9348,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -9387,13 +9387,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="O61" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R61" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.0251936090092966</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -9426,40 +9426,330 @@
       </c>
       <c r="AV61" t="inlineStr">
         <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA61" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB61" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC61" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>scrub-typhus</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>恙虫病</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" t="n">
+        <v>1</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP62" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr"/>
+      <c r="AT62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV62" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW61" t="inlineStr">
+      <c r="AW62" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
+      <c r="AX62" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY61" t="inlineStr">
+      <c r="AY62" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
+      <c r="AZ62" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA61" t="inlineStr">
+      <c r="BA62" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB61" t="inlineStr">
+      <c r="BB62" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC61" t="inlineStr">
+      <c r="BC62" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>scrub-typhus</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>恙虫病</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP63" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr"/>
+      <c r="AT63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV63" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA63" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB63" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC63" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -9498,7 +9788,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -9581,7 +9871,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
@@ -9591,7 +9881,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">
@@ -9643,7 +9933,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d058/2026-2029.xlsx
+++ b/diseases/d058/2026-2029.xlsx
@@ -8372,13 +8372,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O54" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R54" t="n">
-        <v>0.03294548870446478</v>
+        <v>0.03488345862825683</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -9387,13 +9387,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O61" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="R61" t="n">
-        <v>0.0251936090092966</v>
+        <v>0.03682142855204888</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -9752,6 +9752,296 @@
       <c r="BC63" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>scrub-typhus</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>恙虫病</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP64" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr"/>
+      <c r="AT64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV64" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA64" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB64" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC64" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>scrub-typhus</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>恙虫病</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP65" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr"/>
+      <c r="AT65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV65" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA65" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC65" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -9788,7 +10078,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -9871,7 +10161,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10">
@@ -9881,7 +10171,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
@@ -9933,7 +10223,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>343</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d058/2026-2029.xlsx
+++ b/diseases/d058/2026-2029.xlsx
@@ -9387,13 +9387,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O61" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R61" t="n">
-        <v>0.03682142855204888</v>
+        <v>0.04069736839963296</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -9928,12 +9928,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -9958,12 +9958,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N65" t="n">
@@ -10006,40 +10006,185 @@
       </c>
       <c r="AV65" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA65" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC65" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>scrub-typhus</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>恙虫病</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP66" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr"/>
+      <c r="AT66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV66" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW65" t="inlineStr">
+      <c r="AW66" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
+      <c r="AX66" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY65" t="inlineStr">
+      <c r="AY66" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
+      <c r="AZ66" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA65" t="inlineStr">
+      <c r="BA66" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB65" t="inlineStr">
+      <c r="BB66" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC65" t="inlineStr">
+      <c r="BC66" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -10161,7 +10306,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -10171,7 +10316,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11">
@@ -10223,7 +10368,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d058/2026-2029.xlsx
+++ b/diseases/d058/2026-2029.xlsx
@@ -10112,13 +10112,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d058/2026-2029.xlsx
+++ b/diseases/d058/2026-2029.xlsx
@@ -773,6 +773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -918,6 +923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1803,6 +1818,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1948,6 +1968,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2096,6 +2121,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2833,6 +2863,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2978,6 +3013,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3126,6 +3166,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3863,6 +3908,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4008,6 +4058,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4153,6 +4208,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4890,6 +4950,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5035,6 +5100,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5180,6 +5250,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6065,6 +6140,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6210,6 +6290,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6355,6 +6440,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7080,6 +7170,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7225,6 +7320,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7370,6 +7470,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8240,6 +8345,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8385,6 +8495,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8530,6 +8645,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9387,17 +9507,22 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O61" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R61" t="n">
-        <v>0.04069736839963296</v>
+        <v>0.04457330824721705</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -10112,17 +10237,22 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R66" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.009689849618960231</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -10368,7 +10498,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d058/2026-2029.xlsx
+++ b/diseases/d058/2026-2029.xlsx
@@ -9507,13 +9507,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O61" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R61" t="n">
-        <v>0.04457330824721705</v>
+        <v>0.0465112781710091</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -10237,13 +10237,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O66" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="R66" t="n">
-        <v>0.009689849618960231</v>
+        <v>0.0251936090092966</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>359</v>
+        <v>368</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d058/2026-2029.xlsx
+++ b/diseases/d058/2026-2029.xlsx
@@ -10237,13 +10237,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="O66" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R66" t="n">
-        <v>0.0251936090092966</v>
+        <v>0.04263533832342501</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -10317,6 +10317,151 @@
       <c r="BC66" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>scrub-typhus</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>恙虫病</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>1</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP67" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr"/>
+      <c r="AT67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV67" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA67" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB67" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC67" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -10353,7 +10498,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -10436,7 +10581,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10">
@@ -10446,7 +10591,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
@@ -10498,7 +10643,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>368</v>
+        <v>378</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d058/2026-2029.xlsx
+++ b/diseases/d058/2026-2029.xlsx
@@ -9507,13 +9507,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O61" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R61" t="n">
-        <v>0.0465112781710091</v>
+        <v>0.04844924809480115</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -10237,13 +10237,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="O66" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="R66" t="n">
-        <v>0.04263533832342501</v>
+        <v>0.06976691725651366</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>378</v>
+        <v>393</v>
       </c>
     </row>
     <row r="16">
